--- a/admin/template/pay_template.xlsx
+++ b/admin/template/pay_template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA6190EA-543E-4AEC-925F-60A537EE1F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0947AA10-9780-405E-B227-97E2C4A4925F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>审批编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -155,6 +155,14 @@
   </si>
   <si>
     <t>{.payAmount}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>项目名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.project}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -490,106 +498,112 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="4" max="4" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="5" max="8" width="14.25" customWidth="1"/>
-    <col min="9" max="9" width="16.875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="14.25" customWidth="1"/>
+    <col min="10" max="10" width="16.875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>7</v>
       </c>
       <c r="B2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" t="s">
         <v>29</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>21</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>22</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>23</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>24</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>10</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>12</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>13</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>14</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>28</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>26</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>11</v>
       </c>
     </row>
